--- a/04_Kernel_Functions/data/comparativa_benchmark_breast_cancer.xlsx
+++ b/04_Kernel_Functions/data/comparativa_benchmark_breast_cancer.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6318</v>
+        <v>4.878</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -471,18 +471,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1821</v>
+        <v>8.444699999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75 / 569</t>
+          <t>358 / 569</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.18</v>
+        <v>62.92</v>
       </c>
       <c r="E3" t="n">
-        <v>95.43000000000001</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.1007</v>
+        <v>17.654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2134</v>
+        <v>5.2436</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
